--- a/samples/customer.xlsx
+++ b/samples/customer.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" mc:Ignorable="x15 xr xr6 xr10 xr2">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zxyxi\PycharmProjects\PythonProject3\temp3\excel_agent\samples\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Git\AIGit\excel AI Github\excel-analytics-agent\samples\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{873B8C1C-3ABF-42B6-B51D-444C8D3F24EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId3"/>
-    <sheet name="Evaluation Warning" sheetId="2" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Evaluation Warning" sheetId="2" r:id="rId2"/>
   </sheets>
-  <definedNames/>
   <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t>Customer</t>
   </si>
@@ -56,9 +56,6 @@
   </si>
   <si>
     <t>H</t>
-  </si>
-  <si>
-    <t>Sales_Cluster</t>
   </si>
   <si>
     <t>Evaluation Only. Created with Aspose.Cells for Python via .NET. Copyright 2003 - 2026 Aspose Pty Ltd.</t>
@@ -68,19 +65,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -107,30 +98,12 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFADD8E6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF90EE90"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -142,118 +115,24 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="6">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment/>
-      <protection/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment/>
-    </xf>
+  <cellXfs count="4">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment/>
-      <protection/>
-    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="6">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Percent" xfId="1" builtinId="5"/>
-    <cellStyle name="Currency" xfId="2" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="3" builtinId="7"/>
-    <cellStyle name="Comma" xfId="4" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="5" builtinId="6"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -263,179 +142,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <c:roundedCorners val="0"/>
-  <c:chart>
-    <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr wrap="square"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="en-US"/>
-              <a:t>Analysis Result</a:t>
-            </a:r>
-          </a:p>
-        </c:rich>
-      </c:tx>
-      <c:layout/>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-      </c:spPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:plotArea>
-      <c:layout/>
-      <c:lineChart>
-        <c:grouping val="standard"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:dLbls>
-            <c:numFmt formatCode="General" sourceLinked="1"/>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="1"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-            <c:showLeaderLines val="0"/>
-          </c:dLbls>
-          <c:cat>
-            <c:strRef>
-              <c:f>Sheet1!$E$15:$E$22</c:f>
-              <c:strCache>
-                <c:ptCount val="8"/>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Sheet1!$F$15:$F$22</c:f>
-              <c:numCache>
-                <c:ptCount val="8"/>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-        </c:ser>
-        <c:marker val="1"/>
-        <c:axId val="44223604"/>
-        <c:axId val="62468121"/>
-      </c:lineChart>
-      <c:catAx>
-        <c:axId val="44223604"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="out"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="62468121"/>
-        <c:crosses val="autoZero"/>
-        <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
-      </c:catAx>
-      <c:valAx>
-        <c:axId val="62468121"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="out"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="44223604"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
-      </c:valAx>
-      <c:spPr>
-        <a:solidFill>
-          <a:srgbClr val="C0C0C0"/>
-        </a:solidFill>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:srgbClr val="808080"/>
-          </a:solidFill>
-        </a:ln>
-      </c:spPr>
-    </c:plotArea>
-    <c:legend>
-      <c:legendPos val="r"/>
-      <c:layout/>
-      <c:overlay val="0"/>
-    </c:legend>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
-  </c:chart>
-</c:chartSpace>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:to>
-    <xdr:graphicFrame>
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="1" name="Chart 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{23D84D53-3CB8-4DEE-BEB2-D63A83A7B128}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr/>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="5886450" y="857250"/>
-        <a:ext cx="8001000" cy="3600450"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="rId1"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -700,131 +406,105 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="E14:G22"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="E14:F22"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="24.25" customWidth="1"/>
+    <col min="1" max="1" width="24.21875" customWidth="1"/>
     <col min="2" max="2" width="26" customWidth="1"/>
     <col min="7" max="7" width="24" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="14" spans="5:7" ht="27.6">
+    <row r="14" spans="5:6" ht="27.6" x14ac:dyDescent="0.25">
       <c r="E14" s="2" t="s">
         <v>0</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="G14" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="15" spans="5:7" ht="13.8">
+    </row>
+    <row r="15" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E15" s="1" t="s">
         <v>2</v>
       </c>
       <c r="F15" s="1">
         <v>100</v>
       </c>
-      <c r="G15" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="5:7" ht="13.8">
+    </row>
+    <row r="16" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E16" s="1" t="s">
         <v>3</v>
       </c>
       <c r="F16" s="1">
         <v>120</v>
       </c>
-      <c r="G16" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="5:7" ht="13.8">
+    </row>
+    <row r="17" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E17" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F17" s="1">
         <v>130</v>
       </c>
-      <c r="G17" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="5:7" ht="13.8">
+    </row>
+    <row r="18" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E18" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F18" s="1">
         <v>5000</v>
       </c>
-      <c r="G18" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="5:7" ht="13.8">
+    </row>
+    <row r="19" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E19" s="1" t="s">
         <v>6</v>
       </c>
       <c r="F19" s="1">
         <v>5200</v>
       </c>
-      <c r="G19" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="5:7" ht="13.8">
+    </row>
+    <row r="20" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E20" s="1" t="s">
         <v>7</v>
       </c>
       <c r="F20" s="1">
         <v>5300</v>
       </c>
-      <c r="G20" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="5:7" ht="13.8">
+    </row>
+    <row r="21" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E21" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F21" s="1">
         <v>300</v>
       </c>
-      <c r="G21" s="5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="22" spans="5:7" ht="13.8">
+    </row>
+    <row r="22" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E22" s="1" t="s">
         <v>9</v>
       </c>
       <c r="F22" s="1">
         <v>350</v>
       </c>
-      <c r="G22" s="5">
-        <v>2</v>
-      </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4E54BF6-3EEE-41C6-9988-3CAACB68BAA6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4E54BF6-3EEE-41C6-9988-3CAACB68BAA6}">
   <dimension ref="A5"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="5" spans="1:1" ht="23.25" customHeight="1">
-      <c r="A5" s="6" t="s">
-        <v>11</v>
+    <row r="5" spans="1:1" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>